--- a/output/pdf_financials_xlsx/AAV.xlsx
+++ b/output/pdf_financials_xlsx/AAV.xlsx
@@ -953,31 +953,31 @@
         <v>0</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0</v>
+        <v>5.837</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0</v>
+        <v>6.387</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0</v>
+        <v>2.583</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0</v>
+        <v>4.69</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>0</v>
+        <v>27.53</v>
       </c>
       <c r="O9" s="3" t="n">
-        <v>0</v>
+        <v>106.257</v>
       </c>
       <c r="P9" s="3" t="n">
-        <v>0</v>
+        <v>42.432</v>
       </c>
       <c r="Q9" s="3" t="n">
-        <v>0</v>
+        <v>52.471</v>
       </c>
       <c r="R9" s="1" t="inlineStr">
         <is>
@@ -8233,19 +8233,19 @@
         <v>0</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>-2.091</v>
+        <v>-1.339</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>-3.006</v>
+        <v>0.049</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>-0.377</v>
+        <v>-0.196</v>
       </c>
       <c r="G118" s="3" t="n">
         <v>-6.831</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>-3.237</v>
+        <v>-3.184</v>
       </c>
       <c r="I118" s="3" t="n">
         <v>-1.192</v>
@@ -8254,7 +8254,7 @@
         <v>-6.001</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>-7.207</v>
+        <v>-7.039</v>
       </c>
       <c r="L118" s="3" t="n">
         <v>-2.097</v>
@@ -43696,7 +43696,11 @@
           <t>Exploration and evaluation expense 7</t>
         </is>
       </c>
-      <c r="D327" t="inlineStr"/>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E327" t="inlineStr">
         <is>
           <t>-</t>
@@ -46650,7 +46654,11 @@
           <t>Exploration and evaluation expense 6</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -53374,7 +53382,11 @@
           <t>Exploration and evaluation expense 9</t>
         </is>
       </c>
-      <c r="D419" t="inlineStr"/>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E419" t="inlineStr">
         <is>
           <t>-</t>
@@ -54832,7 +54844,11 @@
           <t>Exploration and evaluation expense 8</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr"/>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E433" t="inlineStr">
         <is>
           <t>-</t>
@@ -59320,7 +59336,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D476" t="inlineStr"/>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E476" t="inlineStr">
         <is>
           <t>-</t>
@@ -59372,10 +59392,10 @@
         </is>
       </c>
       <c r="O476" s="5" t="n">
-        <v>-2.583</v>
+        <v>2.583</v>
       </c>
       <c r="P476" s="5" t="n">
-        <v>-4.69</v>
+        <v>4.69</v>
       </c>
       <c r="Q476" t="inlineStr">
         <is>
@@ -59383,13 +59403,13 @@
         </is>
       </c>
       <c r="R476" s="5" t="n">
-        <v>-106.257</v>
+        <v>106.257</v>
       </c>
       <c r="S476" s="5" t="n">
-        <v>-42.432</v>
+        <v>42.432</v>
       </c>
       <c r="T476" s="5" t="n">
-        <v>-52.471</v>
+        <v>52.471</v>
       </c>
       <c r="U476" t="inlineStr">
         <is>
@@ -65604,7 +65624,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D536" t="inlineStr"/>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E536" t="inlineStr">
         <is>
           <t>-</t>
@@ -65666,10 +65690,10 @@
         </is>
       </c>
       <c r="Q536" s="5" t="n">
-        <v>-27.53</v>
+        <v>27.53</v>
       </c>
       <c r="R536" s="5" t="n">
-        <v>-106.257</v>
+        <v>106.257</v>
       </c>
       <c r="S536" t="inlineStr">
         <is>
@@ -71502,7 +71526,11 @@
           <t>Royalty expense</t>
         </is>
       </c>
-      <c r="D592" t="inlineStr"/>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E592" t="inlineStr">
         <is>
           <t>-</t>
@@ -71539,13 +71567,13 @@
         </is>
       </c>
       <c r="L592" s="5" t="n">
-        <v>-5.837</v>
+        <v>5.837</v>
       </c>
       <c r="M592" s="5" t="n">
-        <v>-4.9</v>
+        <v>4.9</v>
       </c>
       <c r="N592" s="5" t="n">
-        <v>-6.387</v>
+        <v>6.387</v>
       </c>
       <c r="O592" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AAV.xlsx
+++ b/output/pdf_financials_xlsx/AAV.xlsx
@@ -1184,10 +1184,10 @@
         <v>0</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.829</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-1.446</v>
       </c>
       <c r="Q12" s="3" t="n">
         <v>0</v>
@@ -2311,10 +2311,10 @@
         <v>216.669</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-4.865</v>
+        <v>-4.036</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-36.959</v>
+        <v>-35.513</v>
       </c>
       <c r="Q27" s="1" t="inlineStr">
         <is>
@@ -2447,10 +2447,10 @@
         <v>216.669</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.865</v>
+        <v>-4.036</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-36.959</v>
+        <v>-35.513</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         <v>47.21208383904194</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-0.6227104351677158</v>
+        <v>-0.5166000650230013</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-6.905810492407327</v>
+        <v>-6.635624557397694</v>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
@@ -60792,7 +60792,7 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
@@ -63208,7 +63208,7 @@
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
@@ -64790,7 +64790,7 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">

--- a/output/pdf_financials_xlsx/AAV.xlsx
+++ b/output/pdf_financials_xlsx/AAV.xlsx
@@ -1411,7 +1411,7 @@
         <v>-86.426</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>-44.208</v>
+        <v>-62.324</v>
       </c>
       <c r="E16" s="1" t="inlineStr">
         <is>
@@ -1424,7 +1424,7 @@
         </is>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-3.382</v>
+        <v>-1.76</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-14.69</v>
@@ -1482,16 +1482,16 @@
         <v>-0</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>18.116</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0</v>
+        <v>-46.807</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-28.605</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-1.622</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>30.393</v>
@@ -1500,16 +1500,16 @@
         <v>7.753</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>4.614</v>
+        <v>-4.614</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>-37.285</v>
+        <v>37.285</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>-5.841</v>
+        <v>5.841</v>
       </c>
       <c r="M17" s="3" t="n">
-        <v>19.879</v>
+        <v>-19.879</v>
       </c>
       <c r="N17" s="3" t="n">
         <v>121.092</v>
@@ -1753,8 +1753,10 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G20" s="3" t="n">
-        <v>4.915</v>
+      <c r="G20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H20" s="3" t="n">
         <v>74.59699999999999</v>
@@ -1821,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0</v>
+        <v>4.915</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0</v>
+        <v>-58.894</v>
       </c>
       <c r="I21" s="3" t="n">
         <v>0</v>
@@ -2274,7 +2276,7 @@
         <v>-86.426</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-44.208</v>
+        <v>-62.324</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -2287,7 +2289,7 @@
         </is>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-3.382</v>
+        <v>-1.76</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-14.69</v>
@@ -2378,13 +2380,13 @@
         <v>0</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>133.917</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>148.897</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>199.489</v>
       </c>
       <c r="R28" s="1" t="inlineStr">
         <is>
@@ -2410,7 +2412,7 @@
         <v>-86.426</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-44.208</v>
+        <v>-62.324</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -2423,7 +2425,7 @@
         </is>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-3.382</v>
+        <v>-1.76</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-14.69</v>
@@ -2447,10 +2449,10 @@
         <v>216.669</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-4.036</v>
+        <v>129.881</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-35.513</v>
+        <v>113.384</v>
       </c>
       <c r="Q29" s="1" t="inlineStr">
         <is>
@@ -2481,7 +2483,7 @@
         <v>-24.22633597201354</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-13.59234047263269</v>
+        <v>-19.16234680637802</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -2532,10 +2534,10 @@
         <v>47.21208383904194</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>-0.5166000650230013</v>
+        <v>16.62451264748573</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>-6.635624557397694</v>
+        <v>21.18586587491848</v>
       </c>
       <c r="Q30" s="1" t="inlineStr">
         <is>
@@ -2566,7 +2568,7 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>-0</v>
+        <v>-29.06745395032411</v>
       </c>
       <c r="E31" s="1" t="inlineStr">
         <is>
@@ -2579,7 +2581,7 @@
         </is>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-92.15909090909091</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-206.8958475153165</v>
@@ -5107,13 +5109,13 @@
         </is>
       </c>
       <c r="B70" s="3" t="n">
-        <v>0</v>
+        <v>1.747</v>
       </c>
       <c r="C70" s="3" t="n">
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>0</v>
+        <v>0.759</v>
       </c>
       <c r="E70" s="3" t="n">
         <v>0</v>
@@ -5172,13 +5174,13 @@
         </is>
       </c>
       <c r="B71" s="3" t="n">
-        <v>0</v>
+        <v>1.747</v>
       </c>
       <c r="C71" s="3" t="n">
-        <v>0</v>
+        <v>1.375</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>0</v>
+        <v>0.759</v>
       </c>
       <c r="E71" s="3" t="n">
         <v>0</v>
@@ -5432,13 +5434,13 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>111.848</v>
+        <v>110.101</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>88.387</v>
+        <v>87.012</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>70.572</v>
+        <v>69.813</v>
       </c>
       <c r="E75" s="3" t="n">
         <v>3.646</v>
@@ -5756,20 +5758,14 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.001445578160930002</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.001112635084014064</v>
+      </c>
+      <c r="D80" s="3" t="n">
+        <v>0.000628214009917339</v>
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
@@ -7096,13 +7092,13 @@
         <v>0</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>133.917</v>
       </c>
       <c r="P100" s="3" t="n">
-        <v>0</v>
+        <v>148.897</v>
       </c>
       <c r="Q100" s="3" t="n">
-        <v>0</v>
+        <v>199.489</v>
       </c>
       <c r="R100" s="1" t="inlineStr">
         <is>
@@ -7542,22 +7538,22 @@
         <v>5.119</v>
       </c>
       <c r="L107" s="3" t="n">
-        <v>0</v>
+        <v>5.162</v>
       </c>
       <c r="M107" s="3" t="n">
-        <v>0</v>
+        <v>5.399</v>
       </c>
       <c r="N107" s="3" t="n">
-        <v>0</v>
+        <v>4.053</v>
       </c>
       <c r="O107" s="3" t="n">
-        <v>0</v>
+        <v>5.524</v>
       </c>
       <c r="P107" s="3" t="n">
-        <v>0</v>
+        <v>6.546</v>
       </c>
       <c r="Q107" s="3" t="n">
-        <v>0</v>
+        <v>3.892</v>
       </c>
       <c r="R107" s="1" t="inlineStr">
         <is>
@@ -8452,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="L121" s="3" t="n">
-        <v>0</v>
+        <v>-0.018</v>
       </c>
       <c r="M121" s="3" t="n">
         <v>0</v>
@@ -30706,7 +30702,11 @@
           <t>Current portion of capital lease obligations (note 4)</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -32600,7 +32600,11 @@
           <t>Current portion of capital lease obligations (note 5)</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E221" s="5" t="n">
         <v>1.747</v>
       </c>
@@ -34178,7 +34182,11 @@
           <t>Share-based compensation expense 21</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -34282,7 +34290,11 @@
           <t>Depreciation and amortization expense 9,11</t>
         </is>
       </c>
-      <c r="D237" t="inlineStr"/>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E237" t="inlineStr">
         <is>
           <t>-</t>
@@ -37494,7 +37506,11 @@
           <t>Share‐based compensation expense 18(b)</t>
         </is>
       </c>
-      <c r="D268" t="inlineStr"/>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E268" t="inlineStr">
         <is>
           <t>-</t>
@@ -37598,7 +37614,11 @@
           <t>Depreciation and amortization expense 8,9</t>
         </is>
       </c>
-      <c r="D269" t="inlineStr"/>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E269" t="inlineStr">
         <is>
           <t>-</t>
@@ -39916,7 +39936,11 @@
           <t>Share‐based compensation expense 19(b)</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -42132,7 +42156,11 @@
           <t>Share-based compensation expense 16</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -43064,7 +43092,11 @@
           <t>Share repurchases 15</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -60366,7 +60398,11 @@
           <t>Depreciation and amortization expense 9,11</t>
         </is>
       </c>
-      <c r="D486" t="inlineStr"/>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E486" t="inlineStr">
         <is>
           <t>-</t>
@@ -62890,7 +62926,11 @@
           <t>Depreciation and amortization expense 8,9</t>
         </is>
       </c>
-      <c r="D510" t="inlineStr"/>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E510" t="inlineStr">
         <is>
           <t>-</t>
@@ -69220,7 +69260,11 @@
           <t>Income tax recovery (expense) 14</t>
         </is>
       </c>
-      <c r="D570" t="inlineStr"/>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E570" t="inlineStr">
         <is>
           <t>-</t>
@@ -72724,7 +72768,11 @@
           <t>Income tax recovery (expense) 12</t>
         </is>
       </c>
-      <c r="D604" t="inlineStr"/>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E604" t="inlineStr">
         <is>
           <t>-</t>
@@ -73850,7 +73898,11 @@
           <t>Income tax recovery (expense) 13</t>
         </is>
       </c>
-      <c r="D615" t="inlineStr"/>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E615" t="inlineStr">
         <is>
           <t>-</t>
@@ -76046,7 +76098,11 @@
           <t>Net loss from discontinued operations 23</t>
         </is>
       </c>
-      <c r="D636" t="inlineStr"/>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E636" t="inlineStr">
         <is>
           <t>-</t>
@@ -78258,7 +78314,11 @@
           <t>Income tax recovery (expense) 14</t>
         </is>
       </c>
-      <c r="D657" t="inlineStr"/>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E657" t="inlineStr">
         <is>
           <t>-</t>
@@ -78468,7 +78528,7 @@
       </c>
       <c r="D659" t="inlineStr">
         <is>
-          <t>NetIncomeContinuousOperations</t>
+          <t>NetIncomeDiscontinuousOperations</t>
         </is>
       </c>
       <c r="E659" t="inlineStr">
@@ -80922,7 +80982,11 @@
           <t>Income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D683" t="inlineStr"/>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E683" t="inlineStr">
         <is>
           <t>-</t>
@@ -82978,7 +83042,11 @@
           <t>Income tax recovery 14</t>
         </is>
       </c>
-      <c r="D703" t="inlineStr"/>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E703" t="inlineStr">
         <is>
           <t>-</t>
@@ -84734,7 +84802,11 @@
           <t>Income tax recovery (expense) 22</t>
         </is>
       </c>
-      <c r="D720" t="inlineStr"/>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E720" t="inlineStr">
         <is>
           <t>-</t>
